--- a/data/trans_orig/P79_n_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R2-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32713</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>33434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>48452</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54483</t>
+          <t>63315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>614389</t>
+          <t>664590</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>602728</t>
+          <t>652907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>622043</t>
+          <t>674639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>705733</t>
+          <t>711848</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>696628</t>
+          <t>700746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>712487</t>
+          <t>718514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1320124</t>
+          <t>1376437</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1306289</t>
+          <t>1361574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1331493</t>
+          <t>1388815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36029</t>
+          <t>41256</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55051</t>
+          <t>57934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>48799</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>37625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>64452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77838</t>
+          <t>90055</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49813</t>
+          <t>72548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98506</t>
+          <t>110291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1156835</t>
+          <t>1007661</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1137813</t>
+          <t>990983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1175005</t>
+          <t>1019723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>916842</t>
+          <t>1022675</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902891</t>
+          <t>1007022</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>927156</t>
+          <t>1033849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2073678</t>
+          <t>2030336</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2053010</t>
+          <t>2010100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2101703</t>
+          <t>2047843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47106</t>
+          <t>46533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>56291</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37304</t>
+          <t>47315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80362</t>
+          <t>82932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>676565</t>
+          <t>773305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660033</t>
+          <t>757904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>686155</t>
+          <t>783747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>905191</t>
+          <t>780486</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>886260</t>
+          <t>765726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>920924</t>
+          <t>790124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1581755</t>
+          <t>1553791</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1557684</t>
+          <t>1532400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1600742</t>
+          <t>1568017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40899</t>
+          <t>49538</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>37219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54486</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40764</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54371</t>
+          <t>62942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>81663</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64457</t>
+          <t>79845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99010</t>
+          <t>117452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>885932</t>
+          <t>940524</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872345</t>
+          <t>924024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896523</t>
+          <t>952843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1054168</t>
+          <t>1070751</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1040561</t>
+          <t>1056099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1065104</t>
+          <t>1082168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1940100</t>
+          <t>2011276</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1922753</t>
+          <t>1991652</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1957306</t>
+          <t>2029259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,102 +2097,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98439</t>
+          <t>122482</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156452</t>
+          <t>177615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>151194</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>130758</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>176427</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>297877</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>264928</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>335361</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>3,64%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>130345</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>102614</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>155967</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>256440</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>217030</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>298878</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -2210,102 +2210,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3333722</t>
+          <t>3386079</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3303365</t>
+          <t>3355147</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3361378</t>
+          <t>3410280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3585760</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3560527</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3606196</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>8416</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6971839</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6934355</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>7004788</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>96,36%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5177</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3581935</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3556313</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3609666</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>8416</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6915657</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6873219</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6955067</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
